--- a/Rohdaten Messung sofern aufgenommen/Übersicht Parameter Messungen.xlsx
+++ b/Rohdaten Messung sofern aufgenommen/Übersicht Parameter Messungen.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://schunkgmbh-my.sharepoint.com/personal/alexander_hoppe_de_schunk_com/Documents/Documents/Praxisarbeiten/T1000/Dokumentation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://schunkgmbh-my.sharepoint.com/personal/alexander_hoppe_de_schunk_com/Documents/Documents/E-Labor/T4-1000-Alexander-Hoppe/Rohdaten Messung sofern aufgenommen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="257" documentId="8_{A33500AD-0E95-4A43-9994-FFBBE5C369AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CAEAC05-C7C1-4AAD-B741-1C3B6F00EE4E}"/>
+  <xr:revisionPtr revIDLastSave="445" documentId="8_{A33500AD-0E95-4A43-9994-FFBBE5C369AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8041017-F6A0-4539-A4A2-B5DBF6B21662}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3696" yWindow="3360" windowWidth="17280" windowHeight="8880" firstSheet="1" activeTab="3" xr2:uid="{947E7A6B-378B-4BE9-93DE-39CF0F84674E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{947E7A6B-378B-4BE9-93DE-39CF0F84674E}"/>
   </bookViews>
   <sheets>
     <sheet name="ACT" sheetId="1" r:id="rId1"/>
     <sheet name="DeltaLine" sheetId="2" r:id="rId2"/>
     <sheet name="Faulhaber" sheetId="3" r:id="rId3"/>
     <sheet name="Maxon" sheetId="4" r:id="rId4"/>
+    <sheet name="Rechner mittlere Stromaufnahme" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="35">
   <si>
     <t>Messungs Nr.</t>
   </si>
@@ -80,23 +81,130 @@
     <t>[mA]</t>
   </si>
   <si>
-    <t>Fahrstrom</t>
-  </si>
-  <si>
     <t>Peakstrom: lösen</t>
   </si>
   <si>
     <t>Peakstrom: spannen</t>
+  </si>
+  <si>
+    <t>spannen</t>
+  </si>
+  <si>
+    <t>Werte:</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>i(0)</t>
+  </si>
+  <si>
+    <t>i(t)</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Messfall</t>
+  </si>
+  <si>
+    <t>Aktion</t>
+  </si>
+  <si>
+    <t>[s]</t>
+  </si>
+  <si>
+    <t>ACT</t>
+  </si>
+  <si>
+    <t>Faulhaber</t>
+  </si>
+  <si>
+    <t>DeltaLine</t>
+  </si>
+  <si>
+    <t>Maxon</t>
+  </si>
+  <si>
+    <t>lösen</t>
+  </si>
+  <si>
+    <t>Steigung</t>
+  </si>
+  <si>
+    <t>t^2</t>
+  </si>
+  <si>
+    <t>I(t)</t>
+  </si>
+  <si>
+    <t>5 oder 6</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>mittel</t>
+    </r>
+  </si>
+  <si>
+    <t>Hilfsgrößen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -128,134 +236,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -650,15 +645,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF584749-72CA-4CDA-B161-C434729A3359}">
-  <dimension ref="B2:K14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:J14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.21875" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" customWidth="1"/>
-    <col min="4" max="4" width="23.44140625" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -681,16 +676,13 @@
         <v>5</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>9</v>
       </c>
@@ -703,16 +695,13 @@
       <c r="J3" t="s">
         <v>11</v>
       </c>
-      <c r="K3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -740,11 +729,8 @@
       <c r="J5">
         <v>1570</v>
       </c>
-      <c r="K5">
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
@@ -773,7 +759,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
@@ -802,7 +788,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>4</v>
       </c>
@@ -831,7 +817,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
@@ -860,7 +846,7 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>6</v>
       </c>
@@ -889,7 +875,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>7</v>
       </c>
@@ -918,7 +904,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>8</v>
       </c>
@@ -947,22 +933,22 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:C14">
-    <cfRule type="cellIs" dxfId="17" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="lessThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -973,7 +959,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1CD89DF-672D-4D03-942A-F572DAACF9FF}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -981,10 +967,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D448297C-7E96-4036-BE40-BA5B15C60DD9}">
-  <dimension ref="B2:K14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:J14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1007,16 +993,13 @@
         <v>5</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>9</v>
       </c>
@@ -1029,16 +1012,13 @@
       <c r="J3" t="s">
         <v>11</v>
       </c>
-      <c r="K3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -1066,11 +1046,8 @@
       <c r="J5">
         <v>718</v>
       </c>
-      <c r="K5">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
@@ -1099,7 +1076,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
@@ -1128,7 +1105,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>4</v>
       </c>
@@ -1157,7 +1134,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
@@ -1186,7 +1163,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>6</v>
       </c>
@@ -1215,7 +1192,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>7</v>
       </c>
@@ -1244,7 +1221,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>8</v>
       </c>
@@ -1273,22 +1250,22 @@
         <v>700</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:C14">
-    <cfRule type="cellIs" dxfId="15" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="lessThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="6" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1298,14 +1275,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CA16C02-AA75-42F7-B9B7-50131D5C5025}">
-  <dimension ref="B2:K14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:J14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="18.6640625" customWidth="1"/>
-    <col min="10" max="10" width="17.5546875" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -1328,16 +1305,13 @@
         <v>5</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
-      </c>
-      <c r="K2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>9</v>
       </c>
@@ -1350,16 +1324,13 @@
       <c r="J3" t="s">
         <v>11</v>
       </c>
-      <c r="K3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -1387,11 +1358,8 @@
       <c r="J5">
         <v>308</v>
       </c>
-      <c r="K5">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
@@ -1420,7 +1388,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
@@ -1449,7 +1417,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>4</v>
       </c>
@@ -1478,7 +1446,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
@@ -1507,7 +1475,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>6</v>
       </c>
@@ -1536,7 +1504,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>7</v>
       </c>
@@ -1565,7 +1533,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>8</v>
       </c>
@@ -1594,25 +1562,462 @@
         <v>810</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:C14">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="7" operator="lessThan">
       <formula>3</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="greaterThan">
       <formula>3</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{876911A9-A725-4CFC-8169-DACA818D4AC9}">
+  <dimension ref="B2:K16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1.6</v>
+      </c>
+      <c r="F5" s="4">
+        <v>500</v>
+      </c>
+      <c r="G5" s="4">
+        <v>160</v>
+      </c>
+      <c r="I5" s="2">
+        <f>(G5-F5)/(2*E5)</f>
+        <v>-106.25</v>
+      </c>
+      <c r="J5" s="2">
+        <f>E5^2</f>
+        <v>2.5600000000000005</v>
+      </c>
+      <c r="K5" s="2">
+        <f t="shared" ref="K5:K16" si="0">(I5*J5)+(F5*E5)</f>
+        <v>528</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>1.4</v>
+      </c>
+      <c r="F6">
+        <v>160</v>
+      </c>
+      <c r="G6">
+        <v>450</v>
+      </c>
+      <c r="H6">
+        <f>(K5+K6)/E6</f>
+        <v>682.14285714285722</v>
+      </c>
+      <c r="I6" s="2">
+        <f>(G6-F6)/(2*E6)</f>
+        <v>103.57142857142858</v>
+      </c>
+      <c r="J6" s="2">
+        <f>E6^2</f>
+        <v>1.9599999999999997</v>
+      </c>
+      <c r="K6" s="2">
+        <f t="shared" si="0"/>
+        <v>427</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>450</v>
+      </c>
+      <c r="G7">
+        <v>160</v>
+      </c>
+      <c r="H7">
+        <f>K7/E7</f>
+        <v>305</v>
+      </c>
+      <c r="I7" s="2">
+        <f>(G7-F7)/(2*E7)</f>
+        <v>-48.333333333333336</v>
+      </c>
+      <c r="J7" s="2">
+        <f>E7^2</f>
+        <v>9</v>
+      </c>
+      <c r="K7" s="2">
+        <f t="shared" si="0"/>
+        <v>915</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>2.1</v>
+      </c>
+      <c r="F8">
+        <v>145</v>
+      </c>
+      <c r="G8">
+        <v>500</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" ref="I8" si="1">(G8-F8)/(2*E8)</f>
+        <v>84.523809523809518</v>
+      </c>
+      <c r="J8" s="2">
+        <f t="shared" ref="J8" si="2">E8^2</f>
+        <v>4.41</v>
+      </c>
+      <c r="K8" s="2">
+        <f t="shared" si="0"/>
+        <v>677.25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9">
+        <v>1.4</v>
+      </c>
+      <c r="F9">
+        <v>340</v>
+      </c>
+      <c r="G9">
+        <v>145</v>
+      </c>
+      <c r="H9">
+        <f>(K8+K9)/E8</f>
+        <v>484.16666666666663</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" ref="I9" si="3">(G9-F9)/(2*E9)</f>
+        <v>-69.642857142857153</v>
+      </c>
+      <c r="J9" s="2">
+        <f t="shared" ref="J9" si="4">E9^2</f>
+        <v>1.9599999999999997</v>
+      </c>
+      <c r="K9" s="2">
+        <f t="shared" si="0"/>
+        <v>339.49999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10">
+        <v>3.4</v>
+      </c>
+      <c r="F10">
+        <v>357</v>
+      </c>
+      <c r="G10">
+        <v>35</v>
+      </c>
+      <c r="H10">
+        <f>K10/E10</f>
+        <v>196</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" ref="I10:I16" si="5">(G10-F10)/(2*E10)</f>
+        <v>-47.352941176470587</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" ref="J10:J16" si="6">E10^2</f>
+        <v>11.559999999999999</v>
+      </c>
+      <c r="K10" s="2">
+        <f t="shared" si="0"/>
+        <v>666.4</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J11" s="2" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K11" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" t="e">
+        <f>(K11+K12)/E11</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I12" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J12" s="2" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K12" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" t="s">
+        <v>32</v>
+      </c>
+      <c r="G13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" t="e">
+        <f>K13/E13</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I13" s="2" t="e">
+        <f t="shared" si="5"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="J13" s="2" t="e">
+        <f t="shared" si="6"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K13" s="2" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="3">
+        <v>8</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>184</v>
+      </c>
+      <c r="G14">
+        <v>80</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="5"/>
+        <v>-17.333333333333332</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" si="6"/>
+        <v>9</v>
+      </c>
+      <c r="K14" s="2">
+        <f t="shared" si="0"/>
+        <v>396</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15">
+        <v>1.8</v>
+      </c>
+      <c r="F15">
+        <v>80</v>
+      </c>
+      <c r="G15">
+        <v>290</v>
+      </c>
+      <c r="H15">
+        <f>(K14+K15)/E15</f>
+        <v>405</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="5"/>
+        <v>58.333333333333329</v>
+      </c>
+      <c r="J15" s="2">
+        <f t="shared" si="6"/>
+        <v>3.24</v>
+      </c>
+      <c r="K15" s="2">
+        <f t="shared" si="0"/>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <v>8</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16">
+        <v>3.2</v>
+      </c>
+      <c r="F16">
+        <v>160</v>
+      </c>
+      <c r="G16">
+        <v>32</v>
+      </c>
+      <c r="H16">
+        <f>K16/E16</f>
+        <v>95.999999999999972</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="5"/>
+        <v>-20</v>
+      </c>
+      <c r="J16" s="2">
+        <f t="shared" si="6"/>
+        <v>10.240000000000002</v>
+      </c>
+      <c r="K16" s="2">
+        <f t="shared" si="0"/>
+        <v>307.19999999999993</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>